--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2130" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{211B54AB-72F0-4619-9BE0-02DF097A9E4E}"/>
+  <xr:revisionPtr revIDLastSave="2131" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AA0E43D-A04F-4F72-8D5B-DF44E828614B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
@@ -3306,11 +3306,11 @@
   <dxfs count="51">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3326,11 +3326,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3386,21 +3386,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="7" tint="-0.499984740745262"/>
       </font>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3416,11 +3416,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3436,11 +3436,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3646,6 +3646,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3666,26 +3676,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3701,6 +3691,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3830,10 +3830,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4298,8 +4294,8 @@
         <v>36509.71</v>
       </c>
       <c r="R2" s="51">
-        <f>IFERROR(SUMIFS(MT!$K:$K, MT!$A:$A, $A2, MT!$C:$C, $C2), 0)</f>
-        <v>337453.87</v>
+        <f>N3</f>
+        <v>26067.41</v>
       </c>
       <c r="S2" s="51">
         <f>IFERROR(SUMIFS(MT!$J:$J, MT!$E:$E, "OUVIDORIA", MT!$A:$A, $A2, MT!$C:$C, $C2), 0)</f>
@@ -20482,26 +20478,26 @@
     <mergeCell ref="H1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" dxfId="39" priority="436" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="438" operator="greaterThan">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="436" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="437" operator="between">
+    <cfRule type="cellIs" dxfId="37" priority="437" operator="between">
       <formula>0.1</formula>
-      <formula>0.7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="438" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I22">
-    <cfRule type="containsText" dxfId="36" priority="328" operator="containsText" text="APENAS BENS">
-      <formula>NOT(ISERROR(SEARCH("APENAS BENS",I3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="329" operator="containsText" text="MAJORITARIAMENTE BENS">
+    <cfRule type="containsText" dxfId="36" priority="329" operator="containsText" text="MAJORITARIAMENTE BENS">
       <formula>NOT(ISERROR(SEARCH("MAJORITARIAMENTE BENS",I3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="330" operator="containsText" text="SERVIÇOS">
+    <cfRule type="containsText" dxfId="35" priority="330" operator="containsText" text="SERVIÇOS">
       <formula>NOT(ISERROR(SEARCH("SERVIÇOS",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="328" operator="containsText" text="APENAS BENS">
+      <formula>NOT(ISERROR(SEARCH("APENAS BENS",I3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J22">
@@ -20592,15 +20588,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P22">
-    <cfRule type="cellIs" dxfId="13" priority="402" operator="lessThan">
-      <formula>0.1</formula>
+    <cfRule type="cellIs" dxfId="13" priority="404" operator="greaterThan">
+      <formula>0.7</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="12" priority="403" operator="between">
       <formula>0.1</formula>
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="404" operator="greaterThan">
-      <formula>0.7</formula>
+    <cfRule type="cellIs" dxfId="11" priority="402" operator="lessThan">
+      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q5">
@@ -20609,11 +20605,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q22">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="APENAS BENS">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="MAJORITARIAMENTE BENS">
+      <formula>NOT(ISERROR(SEARCH("MAJORITARIAMENTE BENS",Q3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="APENAS BENS">
       <formula>NOT(ISERROR(SEARCH("APENAS BENS",Q3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="MAJORITARIAMENTE BENS">
-      <formula>NOT(ISERROR(SEARCH("MAJORITARIAMENTE BENS",Q3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6">
@@ -20639,14 +20635,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S22">
-    <cfRule type="containsText" dxfId="2" priority="14" operator="containsText" text="APENAS BENS">
-      <formula>NOT(ISERROR(SEARCH("APENAS BENS",S3)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="SERVIÇOS">
+      <formula>NOT(ISERROR(SEARCH("SERVIÇOS",S3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="MAJORITARIAMENTE BENS">
       <formula>NOT(ISERROR(SEARCH("MAJORITARIAMENTE BENS",S3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="16" operator="containsText" text="SERVIÇOS">
-      <formula>NOT(ISERROR(SEARCH("SERVIÇOS",S3)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="APENAS BENS">
+      <formula>NOT(ISERROR(SEARCH("APENAS BENS",S3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2131" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AA0E43D-A04F-4F72-8D5B-DF44E828614B}"/>
+  <xr:revisionPtr revIDLastSave="2165" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82C4CCC-C671-4C2C-9829-A5F73616D29E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
+    <workbookView xWindow="-28920" yWindow="-1680" windowWidth="29040" windowHeight="15720" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -4135,7 +4135,7 @@
   <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.3984375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.59765625" style="1" customWidth="1"/>
@@ -4151,12 +4151,11 @@
     <col min="14" max="16" width="19.59765625" style="20" customWidth="1"/>
     <col min="17" max="17" width="29.19921875" style="20" customWidth="1"/>
     <col min="18" max="18" width="17.69921875" style="20" customWidth="1"/>
-    <col min="19" max="19" width="21.69921875" style="20" customWidth="1"/>
-    <col min="20" max="21" width="21.69921875" style="20" hidden="1" customWidth="1"/>
+    <col min="19" max="21" width="21.69921875" style="20" customWidth="1"/>
     <col min="22" max="22" width="16.19921875" style="76" customWidth="1"/>
     <col min="23" max="23" width="10.8984375" style="76" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.19921875" style="76" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="76" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="14.19921875" style="76" customWidth="1"/>
+    <col min="25" max="25" width="13" style="76" customWidth="1"/>
     <col min="26" max="26" width="21.69921875" style="2" customWidth="1"/>
     <col min="27" max="16384" width="9" style="2"/>
   </cols>
@@ -5644,7 +5643,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19C82D0-08F3-47D4-89FB-8BC445800005}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5704,7 +5702,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>44</v>
       </c>
@@ -5745,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>44</v>
       </c>
@@ -5786,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>44</v>
       </c>
@@ -5827,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -5868,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>44</v>
       </c>
@@ -5909,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
@@ -5950,7 +5948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>44</v>
       </c>
@@ -5991,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
@@ -6032,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>44</v>
       </c>
@@ -6073,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
@@ -6114,7 +6112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>44</v>
       </c>
@@ -6157,7 +6155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
@@ -6200,7 +6198,7 @@
         <v>5924.45</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>44</v>
       </c>
@@ -6241,7 +6239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
@@ -6282,7 +6280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>44</v>
       </c>
@@ -6325,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
@@ -6366,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>44</v>
       </c>
@@ -6407,7 +6405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
@@ -6450,7 +6448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>44</v>
       </c>
@@ -6492,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
@@ -6577,7 +6575,7 @@
         <v>14884.16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>44</v>
       </c>
@@ -6704,7 +6702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>44</v>
       </c>
@@ -6747,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>44</v>
       </c>
@@ -6835,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>44</v>
       </c>
@@ -6923,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>44</v>
       </c>
@@ -6964,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>44</v>
       </c>
@@ -7005,7 +7003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>44</v>
       </c>
@@ -7048,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>44</v>
       </c>
@@ -7089,7 +7087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>44</v>
       </c>
@@ -7132,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>44</v>
       </c>
@@ -7173,7 +7171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
         <v>44</v>
       </c>
@@ -7214,7 +7212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>44</v>
       </c>
@@ -7255,7 +7253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
         <v>44</v>
       </c>
@@ -7296,7 +7294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
@@ -7339,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
         <v>44</v>
       </c>
@@ -7382,7 +7380,7 @@
         <v>7267.88</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
@@ -7423,7 +7421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
         <v>44</v>
       </c>
@@ -7464,7 +7462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -7505,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>44</v>
       </c>
@@ -7548,7 +7546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
@@ -7591,7 +7589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
         <v>44</v>
       </c>
@@ -7633,7 +7631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>44</v>
       </c>
@@ -7717,7 +7715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>44</v>
       </c>
@@ -7760,7 +7758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>44</v>
       </c>
@@ -7802,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>44</v>
       </c>
@@ -7887,20 +7885,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L53" xr:uid="{D19C82D0-08F3-47D4-89FB-8BC445800005}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L53" xr:uid="{D19C82D0-08F3-47D4-89FB-8BC445800005}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D820AA79-DBE1-42A0-9210-B49992E6F0A5}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7960,7 +7951,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>46</v>
       </c>
@@ -8041,7 +8032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>46</v>
       </c>
@@ -8082,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>46</v>
       </c>
@@ -8122,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -8163,7 +8154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -8285,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -8326,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>46</v>
       </c>
@@ -8368,7 +8359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>46</v>
       </c>
@@ -8408,7 +8399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>46</v>
       </c>
@@ -8450,7 +8441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>46</v>
       </c>
@@ -8490,7 +8481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>46</v>
       </c>
@@ -8530,7 +8521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>46</v>
       </c>
@@ -8571,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>46</v>
       </c>
@@ -8696,20 +8687,13 @@
       <c r="L21" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18" xr:uid="{D820AA79-DBE1-42A0-9210-B49992E6F0A5}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M18" xr:uid="{D820AA79-DBE1-42A0-9210-B49992E6F0A5}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBB8F27-616C-4167-A382-41D7772815D3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8769,7 +8753,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>48</v>
       </c>
@@ -8811,7 +8795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
@@ -9013,7 +8997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>48</v>
       </c>
@@ -9053,7 +9037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
@@ -9093,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>48</v>
       </c>
@@ -9173,7 +9157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>48</v>
       </c>
@@ -9213,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
@@ -9615,7 +9599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>48</v>
       </c>
@@ -9657,7 +9641,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>48</v>
       </c>
@@ -9697,7 +9681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
@@ -9794,20 +9778,13 @@
       <c r="L29" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M25" xr:uid="{3EBB8F27-616C-4167-A382-41D7772815D3}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M25" xr:uid="{3EBB8F27-616C-4167-A382-41D7772815D3}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A814B8-FBD9-4E5E-950E-D1EDCEABFABC}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9867,7 +9844,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>50</v>
       </c>
@@ -10033,7 +10010,7 @@
         <v>933.32999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>50</v>
       </c>
@@ -10073,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>50</v>
       </c>
@@ -10113,7 +10090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
@@ -10153,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>50</v>
       </c>
@@ -10193,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>50</v>
       </c>
@@ -10233,7 +10210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>50</v>
       </c>
@@ -10273,7 +10250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>50</v>
       </c>
@@ -10313,7 +10290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -10353,7 +10330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>50</v>
       </c>
@@ -10393,7 +10370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>50</v>
       </c>
@@ -10433,7 +10410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>50</v>
       </c>
@@ -10473,7 +10450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>50</v>
       </c>
@@ -10513,7 +10490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>50</v>
       </c>
@@ -10553,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>50</v>
       </c>
@@ -10593,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>50</v>
       </c>
@@ -10633,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>50</v>
       </c>
@@ -10673,7 +10650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>50</v>
       </c>
@@ -10713,7 +10690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>50</v>
       </c>
@@ -10753,7 +10730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>50</v>
       </c>
@@ -10793,7 +10770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
@@ -10833,7 +10810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>50</v>
       </c>
@@ -10913,7 +10890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>50</v>
       </c>
@@ -10953,7 +10930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>50</v>
       </c>
@@ -10993,7 +10970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>50</v>
       </c>
@@ -11073,7 +11050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>50</v>
       </c>
@@ -11153,7 +11130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
         <v>50</v>
       </c>
@@ -11193,7 +11170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>50</v>
       </c>
@@ -11273,7 +11250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>50</v>
       </c>
@@ -11382,20 +11359,13 @@
       <c r="L40" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L38" xr:uid="{36A814B8-FBD9-4E5E-950E-D1EDCEABFABC}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L38" xr:uid="{36A814B8-FBD9-4E5E-950E-D1EDCEABFABC}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D118D3-ABBB-4096-95A3-10DE1CFFD9A8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11455,7 +11425,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>52</v>
       </c>
@@ -11657,7 +11627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>52</v>
       </c>
@@ -11697,7 +11667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>52</v>
       </c>
@@ -11737,7 +11707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
@@ -11777,7 +11747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
@@ -11817,7 +11787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>52</v>
       </c>
@@ -11857,7 +11827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>52</v>
       </c>
@@ -11897,7 +11867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>52</v>
       </c>
@@ -11937,7 +11907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>52</v>
       </c>
@@ -11977,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
@@ -12017,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>52</v>
       </c>
@@ -12057,7 +12027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>52</v>
       </c>
@@ -12097,7 +12067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>52</v>
       </c>
@@ -12137,7 +12107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
@@ -12177,7 +12147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>52</v>
       </c>
@@ -12217,7 +12187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
@@ -12257,7 +12227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>52</v>
       </c>
@@ -12297,7 +12267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>52</v>
       </c>
@@ -12337,7 +12307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>52</v>
       </c>
@@ -12377,7 +12347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>52</v>
       </c>
@@ -12417,7 +12387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>52</v>
       </c>
@@ -12457,7 +12427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
@@ -12497,7 +12467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>52</v>
       </c>
@@ -12537,7 +12507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
@@ -12577,7 +12547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>52</v>
       </c>
@@ -12617,7 +12587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>52</v>
       </c>
@@ -12657,7 +12627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>52</v>
       </c>
@@ -12697,7 +12667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
@@ -12979,7 +12949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>52</v>
       </c>
@@ -13019,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>52</v>
       </c>
@@ -13059,7 +13029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
         <v>52</v>
       </c>
@@ -13099,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>52</v>
       </c>
@@ -13141,7 +13111,7 @@
         <v>-3539.9700000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>52</v>
       </c>
@@ -13183,7 +13153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>52</v>
       </c>
@@ -13223,7 +13193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
         <v>52</v>
       </c>
@@ -13263,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>52</v>
       </c>
@@ -13303,7 +13273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>52</v>
       </c>
@@ -13343,7 +13313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>52</v>
       </c>
@@ -13385,7 +13355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
         <v>52</v>
       </c>
@@ -13425,7 +13395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>52</v>
       </c>
@@ -13467,7 +13437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>52</v>
       </c>
@@ -13507,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>52</v>
       </c>
@@ -13547,7 +13517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>52</v>
       </c>
@@ -13587,7 +13557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>52</v>
       </c>
@@ -13629,7 +13599,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>52</v>
       </c>
@@ -13715,20 +13685,13 @@
       <c r="L59" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M56" xr:uid="{42D118D3-ABBB-4096-95A3-10DE1CFFD9A8}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M56" xr:uid="{42D118D3-ABBB-4096-95A3-10DE1CFFD9A8}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F668D517-0EA8-4538-BB96-E50BAA0D6698}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M63"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13788,7 +13751,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>54</v>
       </c>
@@ -13831,7 +13794,7 @@
         <v>1406.1500000000015</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>54</v>
       </c>
@@ -13871,7 +13834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>54</v>
       </c>
@@ -13913,7 +13876,7 @@
         <v>759.72999999999979</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>54</v>
       </c>
@@ -13956,7 +13919,7 @@
         <v>-382.53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>54</v>
       </c>
@@ -13996,7 +13959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>54</v>
       </c>
@@ -14036,7 +13999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>54</v>
       </c>
@@ -14076,7 +14039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>54</v>
       </c>
@@ -14116,7 +14079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>54</v>
       </c>
@@ -14156,7 +14119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>54</v>
       </c>
@@ -14198,7 +14161,7 @@
         <v>1825.5100000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
@@ -14239,7 +14202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>54</v>
       </c>
@@ -14282,7 +14245,7 @@
         <v>-219.92999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>54</v>
       </c>
@@ -14325,7 +14288,7 @@
         <v>-38.409999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>54</v>
       </c>
@@ -14368,7 +14331,7 @@
         <v>665.02</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>54</v>
       </c>
@@ -14409,7 +14372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>54</v>
       </c>
@@ -14452,7 +14415,7 @@
         <v>16227.330000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>54</v>
       </c>
@@ -14493,7 +14456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>54</v>
       </c>
@@ -14534,7 +14497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>54</v>
       </c>
@@ -14575,7 +14538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>54</v>
       </c>
@@ -14618,7 +14581,7 @@
         <v>7220.4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>54</v>
       </c>
@@ -14659,7 +14622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>54</v>
       </c>
@@ -14700,7 +14663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>54</v>
       </c>
@@ -14741,7 +14704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
@@ -14782,7 +14745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>54</v>
       </c>
@@ -14823,7 +14786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>54</v>
       </c>
@@ -14864,7 +14827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>54</v>
       </c>
@@ -14905,7 +14868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>54</v>
       </c>
@@ -14946,7 +14909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>54</v>
       </c>
@@ -14989,7 +14952,7 @@
         <v>-300.73999999999978</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
@@ -15030,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>54</v>
       </c>
@@ -15073,7 +15036,7 @@
         <v>2004.7399999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>54</v>
       </c>
@@ -15114,7 +15077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
         <v>54</v>
       </c>
@@ -15155,7 +15118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>54</v>
       </c>
@@ -15198,7 +15161,7 @@
         <v>4312.66</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="17" t="s">
         <v>54</v>
       </c>
@@ -15239,7 +15202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>54</v>
       </c>
@@ -15280,7 +15243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>54</v>
       </c>
@@ -15321,7 +15284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>54</v>
       </c>
@@ -15364,7 +15327,7 @@
         <v>1216.19</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>54</v>
       </c>
@@ -15405,7 +15368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>54</v>
       </c>
@@ -15446,7 +15409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
         <v>54</v>
       </c>
@@ -15489,7 +15452,7 @@
         <v>-14344.8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>54</v>
       </c>
@@ -15530,7 +15493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>54</v>
       </c>
@@ -15571,7 +15534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>54</v>
       </c>
@@ -15614,7 +15577,7 @@
         <v>606.72</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
         <v>54</v>
       </c>
@@ -15698,7 +15661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>54</v>
       </c>
@@ -15741,7 +15704,7 @@
         <v>16037.239999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>54</v>
       </c>
@@ -15782,7 +15745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
         <v>54</v>
       </c>
@@ -15823,7 +15786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
@@ -15866,7 +15829,7 @@
         <v>53798</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>54</v>
       </c>
@@ -15909,7 +15872,7 @@
         <v>1783.6</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>54</v>
       </c>
@@ -15951,7 +15914,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -15994,7 +15957,7 @@
         <v>183.4</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
         <v>54</v>
       </c>
@@ -16035,7 +15998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>54</v>
       </c>
@@ -16078,7 +16041,7 @@
         <v>703.52</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
         <v>54</v>
       </c>
@@ -16121,7 +16084,7 @@
         <v>-234.67000000000007</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>54</v>
       </c>
@@ -16164,7 +16127,7 @@
         <v>1868.38</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
         <v>54</v>
       </c>
@@ -16207,7 +16170,7 @@
         <v>1883.2999999999993</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>54</v>
       </c>
@@ -16293,20 +16256,13 @@
       <c r="L63" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L60" xr:uid="{F668D517-0EA8-4538-BB96-E50BAA0D6698}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L60" xr:uid="{F668D517-0EA8-4538-BB96-E50BAA0D6698}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F23310-98D6-41A0-97E8-7BFE177B1FB1}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16366,7 +16322,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>56</v>
       </c>
@@ -16446,7 +16402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>56</v>
       </c>
@@ -16486,7 +16442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
@@ -16526,7 +16482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>56</v>
       </c>
@@ -16766,7 +16722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>56</v>
       </c>
@@ -16886,7 +16842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>56</v>
       </c>
@@ -17046,7 +17002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>56</v>
       </c>
@@ -17086,7 +17042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>56</v>
       </c>
@@ -17166,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>56</v>
       </c>
@@ -17326,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>56</v>
       </c>
@@ -17406,7 +17362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>56</v>
       </c>
@@ -17446,7 +17402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>56</v>
       </c>
@@ -17486,7 +17442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>56</v>
       </c>
@@ -17528,7 +17484,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>56</v>
       </c>
@@ -17608,7 +17564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>56</v>
       </c>
@@ -17787,13 +17743,7 @@
       <c r="L41" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M34" xr:uid="{E4F23310-98D6-41A0-97E8-7BFE177B1FB1}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M34" xr:uid="{E4F23310-98D6-41A0-97E8-7BFE177B1FB1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17801,7 +17751,6 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB30EC91-FBBE-4B9C-9582-4466E1C8CEC0}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17861,7 +17810,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>60</v>
       </c>
@@ -17901,7 +17850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>60</v>
       </c>
@@ -17983,7 +17932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>60</v>
       </c>
@@ -18023,7 +17972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>60</v>
       </c>
@@ -18063,7 +18012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>60</v>
       </c>
@@ -18103,7 +18052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
@@ -18143,7 +18092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>60</v>
       </c>
@@ -18186,7 +18135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>60</v>
       </c>
@@ -18229,7 +18178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>60</v>
       </c>
@@ -18272,7 +18221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>60</v>
       </c>
@@ -18315,7 +18264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>60</v>
       </c>
@@ -18356,7 +18305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>60</v>
       </c>
@@ -18399,7 +18348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>60</v>
       </c>
@@ -18442,7 +18391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>60</v>
       </c>
@@ -18483,7 +18432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>60</v>
       </c>
@@ -18524,7 +18473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>60</v>
       </c>
@@ -18565,7 +18514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>60</v>
       </c>
@@ -18606,7 +18555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>60</v>
       </c>
@@ -18649,7 +18598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>60</v>
       </c>
@@ -18690,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>60</v>
       </c>
@@ -18731,7 +18680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>60</v>
       </c>
@@ -18772,7 +18721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>60</v>
       </c>
@@ -18858,13 +18807,7 @@
       <c r="L27" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M24" xr:uid="{EB30EC91-FBBE-4B9C-9582-4466E1C8CEC0}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M24" xr:uid="{EB30EC91-FBBE-4B9C-9582-4466E1C8CEC0}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -23575,7 +23518,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974C025-C5ED-4C0E-BA99-8AE531702F50}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -23635,7 +23577,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>32</v>
       </c>
@@ -23717,7 +23659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>32</v>
       </c>
@@ -23759,7 +23701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>32</v>
       </c>
@@ -23843,7 +23785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
@@ -23931,7 +23873,7 @@
         <v>578.15999999999985</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>32</v>
       </c>
@@ -24015,7 +23957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>32</v>
       </c>
@@ -24056,7 +23998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
@@ -24144,7 +24086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>32</v>
       </c>
@@ -24228,7 +24170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -24312,7 +24254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>32</v>
       </c>
@@ -24356,7 +24298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>32</v>
       </c>
@@ -24526,7 +24468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>32</v>
       </c>
@@ -24569,7 +24511,7 @@
         <v>4.0000000008149073E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>32</v>
       </c>
@@ -24612,7 +24554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>32</v>
       </c>
@@ -24653,7 +24595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>32</v>
       </c>
@@ -24723,20 +24665,13 @@
       <c r="L28" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M26" xr:uid="{B974C025-C5ED-4C0E-BA99-8AE531702F50}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M26" xr:uid="{B974C025-C5ED-4C0E-BA99-8AE531702F50}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F726102-51C5-4B3B-B3C5-84F08488457B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -24796,7 +24731,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>34</v>
       </c>
@@ -24880,7 +24815,7 @@
         <v>163.8100000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
@@ -24922,7 +24857,7 @@
         <v>196.63999999999987</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>34</v>
       </c>
@@ -24964,7 +24899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>34</v>
       </c>
@@ -25048,7 +24983,7 @@
         <v>5340.6600000000035</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>34</v>
       </c>
@@ -25220,7 +25155,7 @@
         <v>3335.2000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>34</v>
       </c>
@@ -25262,7 +25197,7 @@
         <v>163.8100000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>34</v>
       </c>
@@ -25306,7 +25241,7 @@
         <v>1531.5999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>34</v>
       </c>
@@ -25350,7 +25285,7 @@
         <v>1312.7999999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>34</v>
       </c>
@@ -25438,7 +25373,7 @@
         <v>1224.1999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -25482,7 +25417,7 @@
         <v>1101.7799999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>34</v>
       </c>
@@ -25611,32 +25546,29 @@
       <c r="L24" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18" xr:uid="{4F726102-51C5-4B3B-B3C5-84F08488457B}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M18" xr:uid="{4F726102-51C5-4B3B-B3C5-84F08488457B}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" customWidth="1"/>
-    <col min="7" max="7" width="43.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.19921875" customWidth="1"/>
-    <col min="11" max="11" width="24.19921875" style="85" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.59765625" style="43" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30" style="85" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.59765625" style="43" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
@@ -25724,7 +25656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -25768,7 +25700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>37</v>
       </c>
@@ -25898,7 +25830,7 @@
         <v>2599.1400000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
@@ -25986,7 +25918,7 @@
         <v>511.77000000000044</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -26072,7 +26004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
@@ -26114,7 +26046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
@@ -26156,7 +26088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
@@ -26200,7 +26132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
@@ -26286,7 +26218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>37</v>
       </c>
@@ -26330,7 +26262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -26418,7 +26350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
@@ -26462,7 +26394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>37</v>
       </c>
@@ -26506,7 +26438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -26550,7 +26482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>37</v>
       </c>
@@ -26638,7 +26570,7 @@
         <v>361.05999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
@@ -26726,7 +26658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
@@ -26770,7 +26702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>37</v>
       </c>
@@ -26858,7 +26790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>37</v>
       </c>
@@ -26902,7 +26834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
@@ -26990,7 +26922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
@@ -27078,7 +27010,7 @@
         <v>485.05999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -27122,7 +27054,7 @@
         <v>485.05999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>37</v>
       </c>
@@ -27210,7 +27142,7 @@
         <v>1391.2399999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -27254,7 +27186,7 @@
         <v>1391.2399999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>37</v>
       </c>
@@ -27298,7 +27230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
@@ -27342,7 +27274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>37</v>
       </c>
@@ -27386,7 +27318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>37</v>
       </c>
@@ -27562,7 +27494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
@@ -27606,7 +27538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
@@ -27650,7 +27582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
@@ -27694,7 +27626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>37</v>
       </c>
@@ -27738,7 +27670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
@@ -27782,7 +27714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
@@ -27826,7 +27758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
@@ -27871,20 +27803,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CF666E-167E-4E15-8541-0D1533A82BC2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -27944,7 +27869,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>40</v>
       </c>
@@ -27986,7 +27911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>40</v>
       </c>
@@ -28028,7 +27953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>40</v>
       </c>
@@ -28070,7 +27995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>40</v>
       </c>
@@ -28112,7 +28037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
         <v>40</v>
       </c>
@@ -28238,7 +28163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>40</v>
       </c>
@@ -28280,7 +28205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
         <v>40</v>
       </c>
@@ -28322,7 +28247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>40</v>
       </c>
@@ -28364,7 +28289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>40</v>
       </c>
@@ -28406,7 +28331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>40</v>
       </c>
@@ -28490,7 +28415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>40</v>
       </c>
@@ -28574,7 +28499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>40</v>
       </c>
@@ -28616,7 +28541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
         <v>40</v>
       </c>
@@ -28658,7 +28583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>40</v>
       </c>
@@ -28742,7 +28667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>40</v>
       </c>
@@ -29120,7 +29045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
         <v>40</v>
       </c>
@@ -29162,7 +29087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -29246,7 +29171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>40</v>
       </c>
@@ -29288,7 +29213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>40</v>
       </c>
@@ -29330,7 +29255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>40</v>
       </c>
@@ -29414,7 +29339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>40</v>
       </c>
@@ -29498,7 +29423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>40</v>
       </c>
@@ -29540,7 +29465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="37" t="s">
         <v>40</v>
       </c>
@@ -29624,7 +29549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="37" t="s">
         <v>40</v>
       </c>
@@ -29666,7 +29591,7 @@
         <v>-4590.2199999999993</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>40</v>
       </c>
@@ -29708,7 +29633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>40</v>
       </c>
@@ -29792,7 +29717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>40</v>
       </c>
@@ -29876,7 +29801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>40</v>
       </c>
@@ -29918,7 +29843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
         <v>40</v>
       </c>
@@ -29960,7 +29885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
         <v>40</v>
       </c>
@@ -30044,7 +29969,7 @@
         <v>-61088</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="37" t="s">
         <v>40</v>
       </c>
@@ -30086,7 +30011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
         <v>40</v>
       </c>
@@ -30170,7 +30095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>40</v>
       </c>
@@ -30296,7 +30221,7 @@
         <v>890.01000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="37" t="s">
         <v>40</v>
       </c>
@@ -30380,7 +30305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="37" t="s">
         <v>40</v>
       </c>
@@ -30464,7 +30389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="37" t="s">
         <v>40</v>
       </c>
@@ -30506,7 +30431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>40</v>
       </c>
@@ -30590,7 +30515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>40</v>
       </c>
@@ -30674,7 +30599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>40</v>
       </c>
@@ -30758,7 +30683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
         <v>40</v>
       </c>
@@ -30884,7 +30809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="37" t="s">
         <v>40</v>
       </c>
@@ -31025,20 +30950,13 @@
       <c r="L77" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M73" xr:uid="{D1CF666E-167E-4E15-8541-0D1533A82BC2}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M73" xr:uid="{D1CF666E-167E-4E15-8541-0D1533A82BC2}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E93C9250-D4D5-4EF6-8EF9-5EADAF8441B4}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -31098,7 +31016,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>42</v>
       </c>
@@ -31139,7 +31057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>42</v>
       </c>
@@ -31180,7 +31098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>42</v>
       </c>
@@ -31223,7 +31141,7 @@
         <v>354497.68000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>42</v>
       </c>
@@ -31267,7 +31185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>42</v>
       </c>
@@ -31310,7 +31228,7 @@
         <v>46233.82</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
@@ -31353,7 +31271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>42</v>
       </c>
@@ -31396,7 +31314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
@@ -31439,7 +31357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>42</v>
       </c>
@@ -31482,7 +31400,7 @@
         <v>32765.74</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>42</v>
       </c>
@@ -31525,7 +31443,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
@@ -31568,7 +31486,7 @@
         <v>30700.080000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>42</v>
       </c>
@@ -31654,7 +31572,7 @@
         <v>7.1700000000000728</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>42</v>
       </c>
@@ -31697,7 +31615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>42</v>
       </c>
@@ -31740,7 +31658,7 @@
         <v>7092.59</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>42</v>
       </c>
@@ -31826,7 +31744,7 @@
         <v>4342</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>42</v>
       </c>
@@ -31912,7 +31830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
@@ -31955,7 +31873,7 @@
         <v>347.88000000000011</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>42</v>
       </c>
@@ -32041,7 +31959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
@@ -32128,7 +32046,7 @@
         <v>266.25</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>42</v>
       </c>
@@ -32171,7 +32089,7 @@
         <v>-1317.6800000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
@@ -32214,7 +32132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>42</v>
       </c>
@@ -32257,7 +32175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
@@ -32300,7 +32218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>42</v>
       </c>
@@ -32343,7 +32261,7 @@
         <v>334737.5</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
@@ -32386,7 +32304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>42</v>
       </c>
@@ -32429,7 +32347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
@@ -32472,7 +32390,7 @@
         <v>-1575</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
         <v>42</v>
       </c>
@@ -32515,7 +32433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>42</v>
       </c>
@@ -32558,7 +32476,7 @@
         <v>33273.33</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="17" t="s">
         <v>42</v>
       </c>
@@ -32601,7 +32519,7 @@
         <v>218800</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>42</v>
       </c>
@@ -32644,7 +32562,7 @@
         <v>57024.4</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>42</v>
       </c>
@@ -32730,7 +32648,7 @@
         <v>493.98999999999978</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>42</v>
       </c>
@@ -32816,7 +32734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="6" t="s">
         <v>27</v>
@@ -32856,7 +32774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
         <v>27</v>
@@ -32895,7 +32813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="6" t="s">
         <v>27</v>
@@ -32935,7 +32853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
         <v>27</v>
@@ -33097,13 +33015,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L48" xr:uid="{E93C9250-D4D5-4EF6-8EF9-5EADAF8441B4}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="OUVIDORIA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L48" xr:uid="{E93C9250-D4D5-4EF6-8EF9-5EADAF8441B4}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2165" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82C4CCC-C671-4C2C-9829-A5F73616D29E}"/>
+  <xr:revisionPtr revIDLastSave="2166" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB6E2290-0730-4100-8F0A-106AFAF18C10}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1680" windowWidth="29040" windowHeight="15720" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -2835,7 +2835,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3295,6 +3295,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3832,6 +3835,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -22233,8 +22240,9 @@
       <c r="K23" s="53">
         <v>3270.64</v>
       </c>
-      <c r="L23" s="15">
-        <v>7221.32</v>
+      <c r="L23" s="159">
+        <f>J23-K23</f>
+        <v>3950.68</v>
       </c>
       <c r="M23" s="58">
         <f t="shared" si="0"/>
@@ -25571,7 +25579,7 @@
     <col min="13" max="13" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2166" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB6E2290-0730-4100-8F0A-106AFAF18C10}"/>
+  <xr:revisionPtr revIDLastSave="2168" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ED6A7D5-9BC1-4D24-B994-386CDD437988}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -25561,6 +25561,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -25620,7 +25621,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>37</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -25708,7 +25709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>37</v>
       </c>
@@ -25750,7 +25751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>37</v>
       </c>
@@ -25794,7 +25795,7 @@
         <v>9.0949470177292824E-13</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>37</v>
       </c>
@@ -25838,7 +25839,7 @@
         <v>2599.1400000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
@@ -25882,7 +25883,7 @@
         <v>2425.8599999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>37</v>
       </c>
@@ -25926,7 +25927,7 @@
         <v>511.77000000000044</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -25970,7 +25971,7 @@
         <v>511.77000000000044</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>37</v>
       </c>
@@ -26012,7 +26013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
@@ -26054,7 +26055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
@@ -26096,7 +26097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
@@ -26140,7 +26141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
@@ -26182,7 +26183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
@@ -26226,7 +26227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>37</v>
       </c>
@@ -26270,7 +26271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -26314,7 +26315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
@@ -26358,7 +26359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
@@ -26402,7 +26403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>37</v>
       </c>
@@ -26446,7 +26447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -26490,7 +26491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>37</v>
       </c>
@@ -26534,7 +26535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
@@ -26578,7 +26579,7 @@
         <v>361.05999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
@@ -26622,7 +26623,7 @@
         <v>361.05999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
         <v>37</v>
       </c>
@@ -26666,7 +26667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
@@ -26710,7 +26711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>37</v>
       </c>
@@ -26754,7 +26755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
@@ -26798,7 +26799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>37</v>
       </c>
@@ -26842,7 +26843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
@@ -26886,7 +26887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>37</v>
       </c>
@@ -26930,7 +26931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
@@ -27062,7 +27063,7 @@
         <v>485.05999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>37</v>
       </c>
@@ -27106,7 +27107,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
@@ -27150,7 +27151,7 @@
         <v>1391.2399999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -27194,7 +27195,7 @@
         <v>1391.2399999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>37</v>
       </c>
@@ -27238,7 +27239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
@@ -27282,7 +27283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>37</v>
       </c>
@@ -27326,7 +27327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>37</v>
       </c>
@@ -27370,7 +27371,7 @@
         <v>9.0949470177292824E-13</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
@@ -27414,7 +27415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
@@ -27458,7 +27459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
@@ -27502,7 +27503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
@@ -27546,7 +27547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
@@ -27590,7 +27591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
@@ -27678,7 +27679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
@@ -27722,7 +27723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
@@ -27766,7 +27767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
@@ -27811,7 +27812,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}"/>
+  <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Notebook 4 núcleos 2.4ghz ram ddr 4 8gb"/>
+        <filter val="Notebook com tela de 15'"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2168" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ED6A7D5-9BC1-4D24-B994-386CDD437988}"/>
+  <xr:revisionPtr revIDLastSave="2169" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C181FC70-5DD2-431A-AA6A-F817BB2D343E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
@@ -26055,7 +26055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
@@ -26975,7 +26975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>37</v>
       </c>
@@ -27019,7 +27019,7 @@
         <v>485.05999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -27635,7 +27635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>37</v>
       </c>
@@ -27815,8 +27815,7 @@
   <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
     <filterColumn colId="6">
       <filters>
-        <filter val="Notebook 4 núcleos 2.4ghz ram ddr 4 8gb"/>
-        <filter val="Notebook com tela de 15'"/>
+        <filter val="Desktop para edição de video"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2169" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C181FC70-5DD2-431A-AA6A-F817BB2D343E}"/>
+  <xr:revisionPtr revIDLastSave="2170" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94B4A7C-8EC7-4ECB-8B75-01857993ABD8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
@@ -26055,7 +26055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
@@ -26975,7 +26975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>37</v>
       </c>
@@ -27019,7 +27019,7 @@
         <v>485.05999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -27635,7 +27635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>37</v>
       </c>
@@ -27815,7 +27815,8 @@
   <autoFilter ref="A1:M51" xr:uid="{00F58443-0A8A-4CC5-B51E-2EE000BEE000}">
     <filterColumn colId="6">
       <filters>
-        <filter val="Desktop para edição de video"/>
+        <filter val="Notebook 4 núcleos 2.4ghz ram ddr 4 8gb"/>
+        <filter val="Notebook com tela de 15'"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Planilhas/gestao_financeira_ouvidoria.xlsx
+++ b/Planilhas/gestao_financeira_ouvidoria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2170" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94B4A7C-8EC7-4ECB-8B75-01857993ABD8}"/>
+  <xr:revisionPtr revIDLastSave="2174" documentId="121_{5868839F-5262-4ADE-9247-AEFBBF16C63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD7D9F8-2F52-40B6-B5DF-C3A5FD93407F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{44B50A01-45D3-4E57-8B52-1C8142123E50}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -3282,6 +3282,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3295,9 +3298,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -18845,35 +18845,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="155" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="156"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="157"/>
       <c r="D1" s="93"/>
       <c r="E1" s="86"/>
       <c r="F1" s="86"/>
       <c r="G1" s="104"/>
-      <c r="H1" s="154" t="s">
+      <c r="H1" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="157" t="s">
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="158" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="158"/>
-      <c r="P1" s="157" t="s">
+      <c r="O1" s="159"/>
+      <c r="P1" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="157" t="s">
+      <c r="Q1" s="159"/>
+      <c r="R1" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="S1" s="158"/>
+      <c r="S1" s="159"/>
     </row>
     <row r="2" spans="1:19" s="4" customFormat="1" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="96" t="s">
@@ -22240,7 +22240,7 @@
       <c r="K23" s="53">
         <v>3270.64</v>
       </c>
-      <c r="L23" s="159">
+      <c r="L23" s="154">
         <f>J23-K23</f>
         <v>3950.68</v>
       </c>
